--- a/光伏配储项目/电价数据/2026/征程站.xlsx
+++ b/光伏配储项目/电价数据/2026/征程站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.62101</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8308099999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.69852</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6069199999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.6072000000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6110099999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46896</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43677</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42364</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45545</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51661</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40749</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.19507</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.21563</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21061</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17003</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.19603</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25151</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06159000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15905</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24162</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24044</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24527</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22971</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.23533</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.87926</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.21915</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.50992</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.52544</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.53815</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.61807</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.6342100000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7262000000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.25076</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43488</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65454</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.96565</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.57077</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.30746</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.44197</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17399</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.3046</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.3819</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.5706</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.5451699999999999</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.78547</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.83765</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.34914</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.14136</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8653500000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7936299999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75363</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46474</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42388</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7003400000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74459</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86241</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9032899999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48911</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.50718</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49677</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49697</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47961</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46223</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.70357</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.56289</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.66212</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40749</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42886</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50928</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.57773</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85256</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.06765</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5804600000000001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.93425</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8883799999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.55687</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.8349099999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.24055</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05642</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40717</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5841000000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54359</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5376799999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8640599999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60611</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.78271</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.87295</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.23554</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.16018</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.89486</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.28587</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.19005</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.34854</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.13011</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.17476</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.73336</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.06561</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.89359</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.08194</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.00466</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.09532</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.89759</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44692</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81241</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.83225</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44629</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42587</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44088</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33432</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50247</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4802</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44178</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4387799999999999</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46726</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.2072</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26281</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.53363</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.4855</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.48042</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.5658099999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.57328</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.65865</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.62352</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.89783</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.57741</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.69565</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.77564</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.86214</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52276</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5204299999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7784</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6438400000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6342300000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.57698</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45384</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51115</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57699</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.61048</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.57768</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.59929</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23429</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6100599999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7730499999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4728</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51246</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57775</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.73617</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.74094</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.9124099999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48521</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6149</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.47557</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.57636</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60129</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.7417999999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56235</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.90239</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.70973</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5772</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5128200000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64471</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43586</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45413</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34161</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51418</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44516</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44863</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.48492</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.49175</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6559199999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.49599</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.50592</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.22273</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.59165</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48951</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41828</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.43272</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.42743</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.50517</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.7079</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48221</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45562</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.46951</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.53232</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6858500000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.54538</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.76658</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5468999999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.50368</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.44803</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30956</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24239</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26368</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14651</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.07490000000000001</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24363</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.26401</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.25849</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.18103</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24511</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22324</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08451</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.17824</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.13782</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01417</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45687</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.33087</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.45741</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.2486</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21567</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.10479</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22505</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24514</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27459</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.23409</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25834</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10344</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04398</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01179</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20959</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05095</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19575</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.19036</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06374</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06196</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32372</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30076</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45239</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7849400000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87193</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.76602</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.61264</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44874</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44653</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.50554</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.56092</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.65443</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8692300000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46067</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.49679</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.70148</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.45837</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83423</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.51088</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57723</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.55376</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.23437</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33567</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.90549</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23471</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27221</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19431</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24582</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24818</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.4107</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26305</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81174</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38379</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08373</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6533</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.74222</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.60658</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46417</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46804</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.23233</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46975</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14559</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27323</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02851</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25481</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27041</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.48699</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6735099999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.2746</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23835</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.24456</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.23412</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.24109</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21718</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25778</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.20889</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.2094</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.10144</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22741</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.26981</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.10267</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.25269</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26795</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.25352</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27592</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.22471</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20617</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22391</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27551</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27937</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23706</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.2426</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.25409</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.26416</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22618</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.23253</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27519</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.25418</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.25102</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27222</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24579</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22634</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.24791</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.25482</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.23267</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26937</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24722</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28455</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30846</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.27831</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27841</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23804</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.42134</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.48277</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.45557</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.47746</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44726</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.55377</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.48881</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32738</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.24479</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.50319</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.77376</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.46949</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.56557</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.53444</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5985499999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.47283</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.5156499999999999</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.47422</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.72326</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.54013</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.5662999999999999</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.9065700000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.65754</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.51585</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.6137100000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.56969</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.55528</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.74971</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.5567000000000001</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.5687300000000001</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.5859500000000001</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.51591</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.63379</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.42991</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.46364</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.42912</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.48465</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.43205</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.74295</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.54253</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.5665800000000001</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.51681</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.77683</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.47332</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.47666</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49128</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22454</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.19718</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.25148</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.25723</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24624</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24876</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.24624</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.22264</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28782</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.25124</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.26141</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.24011</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22872</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26483</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.44019</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.23491</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33156</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.13362</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.44907</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6406000000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.9665900000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.5587300000000001</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.43115</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.55747</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.42441</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.48508</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.42006</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.5232</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.5572699999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.76288</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.63398</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.72435</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.68187</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.47111</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.86836</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48224</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.77666</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.71053</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5678</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.47868</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.60682</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.5274099999999999</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33252</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48634</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.48268</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.48205</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.50836</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.5295800000000001</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.5664400000000001</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.66579</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6454500000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41648</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.44678</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.45217</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.70073</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40989</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.89843</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.40301</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.45913</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.47259</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.52501</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.61239</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.45288</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.53164</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5192599999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.47809</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5418200000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75549</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6075499999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65446</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.47312</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.37743</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.14868</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.6469600000000001</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.56861</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.48789</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.41993</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.47843</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5364800000000001</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.23685</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27405</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.28161</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25749</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23755</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25755</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26733</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.43011</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23992</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.14863</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.13895</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.13789</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23996</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.13252</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23891</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.13134</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22604</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.23221</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.25336</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22894</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.23256</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23619</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.12719</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.23981</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.12666</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.11155</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.25433</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23598</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.21606</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.10324</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27333</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11965</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27463</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24863</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.19171</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01756</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24534</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25605</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.27151</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24983</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25921</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.23473</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.23366</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.27342</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26557</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.15742</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23967</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23596</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.11491</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24492</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25906</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.25294</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.14214</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.10888</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.11711</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.1171</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.11525</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.11525</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.11636</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.10676</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.11525</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.11542</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.2295</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.10895</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.10885</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.11985</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07745999999999999</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25601</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.12085</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00283</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00016</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14159</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04084</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02932</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04603</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00092</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03851</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02228</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03638</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19969</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.11822</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.30127</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.53988</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.22234</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23819</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24231</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23876</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.12208</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.2348</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22032</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12515</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.08989</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.10799</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.11704</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.13217</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.09745000000000001</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.14232</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.14932</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.16227</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42615</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.11673</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5782200000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86812</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85814</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1093</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.10705</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27519</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.09409000000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00087</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00048</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06691</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.1139</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.66808</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.56956</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.60899</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.09291</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9753099999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.57773</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.7310399999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.6235299999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83104</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82925</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83353</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9312699999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.56692</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.61956</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.57429</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33589</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.40074</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.47639</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.27578</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.4461</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48285</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26782</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.26239</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.24237</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25703</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23852</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.12439</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.25159</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.26213</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25711</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39501</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.56714</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.49295</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42136</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32181</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.47809</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.70609</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.57452</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47499</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.8334600000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.86695</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.29101</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.51432</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.6049500000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.59193</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.18056</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.9080199999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5715399999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6490499999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.49134</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.47304</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22317</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43545</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.47881</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41164</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40255</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50422</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.6056699999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.40037</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.13665</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.64951</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.94151</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53151</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.67845</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.58052</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45705</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.8304199999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7523500000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.90179</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.81235</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.72399</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.48373</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.13801</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.53899</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.5321</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.9143</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.54538</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.47172</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.22861</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.6856100000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.45933</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.93779</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.5714400000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.5128400000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.44966</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.46865</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.43649</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.5213300000000001</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.47671</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.41711</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.57035</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.72054</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5527000000000001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43179</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.49452</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.7149500000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.44159</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.49008</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.44884</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.52507</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3503</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9228</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.52658</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4997799999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.53089</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.5124099999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5212599999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.63428</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.51775</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.48266</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4837</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.46845</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35144</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17582</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14326</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04575</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12094</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22508</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14752</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14406</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19208</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22643</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26024</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15167</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15395</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19575</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14035</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27743</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.53191</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.5948300000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45731</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40461</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37874</v>
       </c>
     </row>
   </sheetData>
